--- a/artfynd/S 3633-2024 artfynd.xlsx
+++ b/artfynd/S 3633-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY71"/>
+  <dimension ref="A1:AZ71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4173182</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91906819</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1001,6 +1016,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104809243</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1115,6 +1135,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103919305</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1229,6 +1254,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103919327</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1343,6 +1373,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103920281</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1457,6 +1492,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103920301</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1571,6 +1611,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103920319</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1685,6 +1730,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103920339</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1799,6 +1849,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103920355</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1913,6 +1968,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103920365</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2027,6 +2087,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103920369</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2141,6 +2206,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103920392</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2255,6 +2325,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103920410</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2369,6 +2444,11 @@
           <t>PÖN0100 fågelinventering</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114257076</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2483,6 +2563,11 @@
           <t>PÖN0100 fågelinventering</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114257077</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2597,6 +2682,11 @@
           <t>PÖN0100 fågelinventering</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114257079</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2711,6 +2801,11 @@
           <t>PÖN0100 fågelinventering</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114257080</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2830,6 +2925,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72833903</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2949,6 +3049,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103920437</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3074,6 +3179,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72834004</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3181,6 +3291,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1602656</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3295,6 +3410,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126460970</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3416,6 +3536,11 @@
           <t>Nordsyd - Naturvärdesinventering åt Svenska kraftnät</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115250333</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3552,6 +3677,11 @@
           <t>PÖN0100 fågelinventering</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114052569</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3664,6 +3794,11 @@
           <t>PÖN0100 fågelinventering</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114176154</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3782,6 +3917,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126461005</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3884,6 +4024,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126461019</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3998,6 +4143,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126461054</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4112,6 +4262,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126461067</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4231,6 +4386,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81113627</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4349,6 +4509,11 @@
           <t>PÖN0100 fågelinventering</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114257039</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4458,6 +4623,11 @@
           <t>PÖN0100 fågelinventering</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114257043</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4560,6 +4730,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79444627</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4661,6 +4836,11 @@
           <t>Nordsyd - Naturvärdesinventering åt Svenska kraftnät</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105132349</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4793,6 +4973,11 @@
           <t>PÖN0100 fågelinventering</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114176007</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4912,6 +5097,11 @@
           <t>PÖN0100 fågelinventering</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114257012</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5031,6 +5221,11 @@
           <t>PÖN0100 fågelinventering</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114257013</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5155,6 +5350,11 @@
           <t>PÖN0100 fågelinventering</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114257015</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5273,6 +5473,11 @@
           <t>PÖN0100 fågelinventering</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114257027</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5391,6 +5596,11 @@
           <t>PÖN0100 fågelinventering</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114257028</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5509,6 +5719,11 @@
           <t>PÖN0100 fågelinventering</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114257029</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5623,6 +5838,11 @@
           <t>PÖN0100 fågelinventering</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114257030</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5741,6 +5961,11 @@
           <t>PÖN0100 fågelinventering</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114257032</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5850,6 +6075,11 @@
           <t>PÖN0100 fågelinventering</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114257042</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5964,6 +6194,11 @@
           <t>PÖN0100 fågelinventering</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114257044</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6078,6 +6313,11 @@
           <t>PÖN0100 fågelinventering</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114257045</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6192,6 +6432,11 @@
           <t>PÖN0100 fågelinventering</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114257047</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6299,6 +6544,11 @@
       <c r="AY50" t="inlineStr">
         <is>
           <t>PÖN0100 fågelinventering</t>
+        </is>
+      </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114257049</t>
         </is>
       </c>
     </row>
@@ -6407,6 +6657,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130340669</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6523,6 +6778,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/399496</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6642,6 +6902,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126434631</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6759,6 +7024,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82806611</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6870,6 +7140,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82808976</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6981,6 +7256,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130340659</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7100,6 +7380,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100204689</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7211,6 +7496,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130340636</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7334,6 +7624,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16850535</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7453,6 +7748,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60117202</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7575,6 +7875,11 @@
       <c r="AY61" t="inlineStr">
         <is>
           <t>PÖN0100 fågelinventering</t>
+        </is>
+      </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114257025</t>
         </is>
       </c>
     </row>
@@ -7684,6 +7989,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124562027</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7799,6 +8109,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124562523</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7897,6 +8212,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5981167</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -8004,6 +8324,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82438838</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8123,6 +8448,11 @@
           <t>PÖN0100 fågelinventering</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114257023</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8247,6 +8577,11 @@
           <t>PÖN0100 fågelinventering</t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114257024</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8379,6 +8714,11 @@
           <t>Däggdjursinventering Surahammar</t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98427004</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8495,6 +8835,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77390604</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8611,6 +8956,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77390610</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8732,8 +9082,85 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118290741</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>